--- a/Semiconductor/PRSO.xlsx
+++ b/Semiconductor/PRSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/Models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F40617-4C71-774D-BD76-02B8CF02B765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3074B0E5-1D55-C744-AE2F-C0FEAB39D895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23480" yWindow="4020" windowWidth="27640" windowHeight="23540" activeTab="1" xr2:uid="{2B0E9291-F618-3A4E-B6D1-6A0F4157E422}"/>
+    <workbookView xWindow="18700" yWindow="2820" windowWidth="27660" windowHeight="23560" activeTab="1" xr2:uid="{2B0E9291-F618-3A4E-B6D1-6A0F4157E422}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t>P</t>
   </si>
@@ -318,6 +318,18 @@
   </si>
   <si>
     <t>mmWave other products</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -531,13 +543,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>5825</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>11651</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>35278</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>141111</xdr:rowOff>
@@ -1184,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7522E82B-D5CC-354F-B760-A8D007B807BB}">
-  <dimension ref="A1:AG53"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1193,25 +1205,26 @@
     <col min="6" max="6" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4" style="1" customWidth="1"/>
-    <col min="13" max="14" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="5.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="4" style="1" customWidth="1"/>
+    <col min="17" max="18" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="31" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="10.83203125" style="1"/>
+    <col min="23" max="25" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="35" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:35">
       <c r="A1" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="10" customFormat="1">
+    <row r="2" spans="1:35" s="10" customFormat="1">
       <c r="C2" s="10" t="s">
         <v>11</v>
       </c>
@@ -1236,139 +1249,151 @@
       <c r="J2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="10">
+      <c r="K2" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q2" s="10">
         <v>2015</v>
       </c>
-      <c r="N2" s="10">
-        <f>+M2+1</f>
+      <c r="R2" s="10">
+        <f>+Q2+1</f>
         <v>2016</v>
       </c>
-      <c r="O2" s="10">
-        <f t="shared" ref="O2:AE2" si="0">+N2+1</f>
+      <c r="S2" s="10">
+        <f t="shared" ref="S2:AI2" si="0">+R2+1</f>
         <v>2017</v>
       </c>
-      <c r="P2" s="10">
+      <c r="T2" s="10">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="U2" s="10">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="R2" s="10">
+      <c r="V2" s="10">
         <f t="shared" si="0"/>
         <v>2020</v>
       </c>
-      <c r="S2" s="10">
+      <c r="W2" s="10">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="T2" s="10">
+      <c r="X2" s="10">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="U2" s="10">
+      <c r="Y2" s="10">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="V2" s="10">
+      <c r="Z2" s="10">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="W2" s="10">
+      <c r="AA2" s="10">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="X2" s="10">
+      <c r="AB2" s="10">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="AC2" s="10">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="AD2" s="10">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="AA2" s="10">
+      <c r="AE2" s="10">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="AB2" s="10">
+      <c r="AF2" s="10">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="AC2" s="10">
+      <c r="AG2" s="10">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="AD2" s="10">
+      <c r="AH2" s="10">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="AE2" s="10">
+      <c r="AI2" s="10">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:35">
       <c r="B3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="S3" s="1">
+      <c r="W3" s="1">
         <v>150</v>
       </c>
-      <c r="T3" s="1">
+      <c r="X3" s="1">
         <v>7722</v>
       </c>
-      <c r="U3" s="1">
+      <c r="Y3" s="1">
         <v>8446</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:35">
       <c r="B4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="1">
+      <c r="W4" s="1">
         <v>3566</v>
       </c>
-      <c r="T4" s="1">
+      <c r="X4" s="1">
         <v>3289</v>
       </c>
-      <c r="U4" s="1">
+      <c r="Y4" s="1">
         <v>2726</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:35">
       <c r="B5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="S5" s="1">
+      <c r="W5" s="1">
         <v>1101</v>
       </c>
-      <c r="T5" s="1">
+      <c r="X5" s="1">
         <v>3170</v>
       </c>
-      <c r="U5" s="1">
+      <c r="Y5" s="1">
         <v>1677</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:35">
       <c r="B6" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="S6" s="1">
+      <c r="W6" s="1">
         <v>89</v>
       </c>
-      <c r="T6" s="1">
+      <c r="X6" s="1">
         <v>18</v>
       </c>
-      <c r="U6" s="1">
+      <c r="Y6" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:35">
       <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1382,7 +1407,7 @@
         <v>4262</v>
       </c>
       <c r="F7" s="1">
-        <f>+U7-SUM(C7:E7)</f>
+        <f>+Y7-SUM(C7:E7)</f>
         <v>1468</v>
       </c>
       <c r="G7" s="1">
@@ -1398,78 +1423,78 @@
         <f>+J9*0.99</f>
         <v>3762</v>
       </c>
-      <c r="M7" s="1">
+      <c r="Q7" s="1">
         <v>2400</v>
       </c>
-      <c r="N7" s="1">
+      <c r="R7" s="1">
         <v>4604</v>
       </c>
-      <c r="O7" s="1">
+      <c r="S7" s="1">
         <v>7833</v>
       </c>
-      <c r="P7" s="1">
+      <c r="T7" s="1">
         <v>15053</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="U7" s="1">
         <v>9377</v>
       </c>
-      <c r="R7" s="1">
+      <c r="V7" s="1">
         <v>1540</v>
       </c>
-      <c r="S7" s="1">
-        <f>SUM(S3:S6)</f>
+      <c r="W7" s="1">
+        <f>SUM(W3:W6)</f>
         <v>4906</v>
       </c>
-      <c r="T7" s="1">
-        <f>SUM(T3:T6)</f>
+      <c r="X7" s="1">
+        <f>SUM(X3:X6)</f>
         <v>14199</v>
       </c>
-      <c r="U7" s="1">
-        <f>SUM(U3:U6)</f>
+      <c r="Y7" s="1">
+        <f>SUM(Y3:Y6)</f>
         <v>12853</v>
       </c>
-      <c r="V7" s="1">
+      <c r="Z7" s="1">
         <f>SUM(G7:J7)</f>
         <v>14358</v>
       </c>
-      <c r="W7" s="1">
-        <f>+V7*0.5</f>
+      <c r="AA7" s="1">
+        <f>+Z7*0.5</f>
         <v>7179</v>
       </c>
-      <c r="X7" s="1">
-        <f>+W7*1.01</f>
+      <c r="AB7" s="1">
+        <f>+AA7*1.01</f>
         <v>7250.79</v>
       </c>
-      <c r="Y7" s="1">
-        <f t="shared" ref="Y7:AE7" si="1">+X7*1.01</f>
+      <c r="AC7" s="1">
+        <f t="shared" ref="AC7:AI7" si="1">+AB7*1.01</f>
         <v>7323.2979000000005</v>
       </c>
-      <c r="Z7" s="1">
+      <c r="AD7" s="1">
         <f t="shared" si="1"/>
         <v>7396.5308790000008</v>
       </c>
-      <c r="AA7" s="1">
+      <c r="AE7" s="1">
         <f t="shared" si="1"/>
         <v>7470.4961877900005</v>
       </c>
-      <c r="AB7" s="1">
+      <c r="AF7" s="1">
         <f t="shared" si="1"/>
         <v>7545.2011496679006</v>
       </c>
-      <c r="AC7" s="1">
+      <c r="AG7" s="1">
         <f t="shared" si="1"/>
         <v>7620.6531611645796</v>
       </c>
-      <c r="AD7" s="1">
+      <c r="AH7" s="1">
         <f t="shared" si="1"/>
         <v>7696.8596927762255</v>
       </c>
-      <c r="AE7" s="1">
+      <c r="AI7" s="1">
         <f t="shared" si="1"/>
         <v>7773.828289703988</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:35">
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1483,7 +1508,7 @@
         <v>219</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" ref="F8:F15" si="2">+U8-SUM(C8:E8)</f>
+        <f t="shared" ref="F8:F15" si="2">+Y8-SUM(C8:E8)</f>
         <v>364</v>
       </c>
       <c r="G8" s="1">
@@ -1499,75 +1524,75 @@
         <f>+J9*0.01</f>
         <v>38</v>
       </c>
-      <c r="M8" s="1">
+      <c r="Q8" s="1">
         <v>1990</v>
       </c>
-      <c r="N8" s="1">
+      <c r="R8" s="1">
         <v>1420</v>
       </c>
-      <c r="O8" s="1">
+      <c r="S8" s="1">
         <v>1009</v>
       </c>
-      <c r="P8" s="1">
+      <c r="T8" s="1">
         <v>1547</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="U8" s="1">
         <v>709</v>
       </c>
-      <c r="R8" s="1">
+      <c r="V8" s="1">
         <v>7550</v>
       </c>
-      <c r="S8" s="1">
+      <c r="W8" s="1">
         <v>773</v>
       </c>
-      <c r="T8" s="1">
+      <c r="X8" s="1">
         <v>669</v>
       </c>
-      <c r="U8" s="1">
+      <c r="Y8" s="1">
         <v>896</v>
       </c>
-      <c r="V8" s="1">
+      <c r="Z8" s="1">
         <f>SUM(G8:J8)</f>
         <v>337</v>
       </c>
-      <c r="W8" s="1">
-        <f>+V8*1.01</f>
+      <c r="AA8" s="1">
+        <f>+Z8*1.01</f>
         <v>340.37</v>
       </c>
-      <c r="X8" s="1">
-        <f t="shared" ref="X8:AE8" si="3">+W8*1.01</f>
+      <c r="AB8" s="1">
+        <f t="shared" ref="AB8:AI8" si="3">+AA8*1.01</f>
         <v>343.77370000000002</v>
       </c>
-      <c r="Y8" s="1">
+      <c r="AC8" s="1">
         <f t="shared" si="3"/>
         <v>347.21143700000005</v>
       </c>
-      <c r="Z8" s="1">
+      <c r="AD8" s="1">
         <f t="shared" si="3"/>
         <v>350.68355137000003</v>
       </c>
-      <c r="AA8" s="1">
+      <c r="AE8" s="1">
         <f t="shared" si="3"/>
         <v>354.19038688370006</v>
       </c>
-      <c r="AB8" s="1">
+      <c r="AF8" s="1">
         <f t="shared" si="3"/>
         <v>357.73229075253704</v>
       </c>
-      <c r="AC8" s="1">
+      <c r="AG8" s="1">
         <f t="shared" si="3"/>
         <v>361.30961366006244</v>
       </c>
-      <c r="AD8" s="1">
+      <c r="AH8" s="1">
         <f t="shared" si="3"/>
         <v>364.92270979666307</v>
       </c>
-      <c r="AE8" s="1">
+      <c r="AI8" s="1">
         <f t="shared" si="3"/>
         <v>368.57193689462969</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="9" customFormat="1">
+    <row r="9" spans="1:35" s="9" customFormat="1">
       <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
@@ -1603,84 +1628,84 @@
         <f>AVERAGE(3.6,4) * 10^3</f>
         <v>3800</v>
       </c>
-      <c r="M9" s="9">
-        <f t="shared" ref="M9:W9" si="5">+SUM(M7:M8)</f>
+      <c r="Q9" s="9">
+        <f t="shared" ref="Q9:AA9" si="5">+SUM(Q7:Q8)</f>
         <v>4390</v>
       </c>
-      <c r="N9" s="9">
+      <c r="R9" s="9">
         <f t="shared" si="5"/>
         <v>6024</v>
       </c>
-      <c r="O9" s="9">
+      <c r="S9" s="9">
         <f t="shared" si="5"/>
         <v>8842</v>
       </c>
-      <c r="P9" s="9">
+      <c r="T9" s="9">
         <f t="shared" si="5"/>
         <v>16600</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="U9" s="9">
         <f t="shared" si="5"/>
         <v>10086</v>
       </c>
-      <c r="R9" s="9">
+      <c r="V9" s="9">
         <f t="shared" si="5"/>
         <v>9090</v>
       </c>
-      <c r="S9" s="9">
+      <c r="W9" s="9">
         <f t="shared" si="5"/>
         <v>5679</v>
       </c>
-      <c r="T9" s="9">
+      <c r="X9" s="9">
         <f t="shared" si="5"/>
         <v>14868</v>
       </c>
-      <c r="U9" s="9">
+      <c r="Y9" s="9">
         <f t="shared" si="5"/>
         <v>13749</v>
       </c>
-      <c r="V9" s="9">
+      <c r="Z9" s="9">
         <f t="shared" si="5"/>
         <v>14695</v>
       </c>
-      <c r="W9" s="9">
+      <c r="AA9" s="9">
         <f t="shared" si="5"/>
         <v>7519.37</v>
       </c>
-      <c r="X9" s="9">
-        <f t="shared" ref="X9:AE9" si="6">+SUM(X7:X8)</f>
+      <c r="AB9" s="9">
+        <f t="shared" ref="AB9:AI9" si="6">+SUM(AB7:AB8)</f>
         <v>7594.5636999999997</v>
       </c>
-      <c r="Y9" s="9">
+      <c r="AC9" s="9">
         <f t="shared" si="6"/>
         <v>7670.5093370000004</v>
       </c>
-      <c r="Z9" s="9">
+      <c r="AD9" s="9">
         <f t="shared" si="6"/>
         <v>7747.2144303700006</v>
       </c>
-      <c r="AA9" s="9">
+      <c r="AE9" s="9">
         <f t="shared" si="6"/>
         <v>7824.6865746737003</v>
       </c>
-      <c r="AB9" s="9">
+      <c r="AF9" s="9">
         <f t="shared" si="6"/>
         <v>7902.9334404204374</v>
       </c>
-      <c r="AC9" s="9">
+      <c r="AG9" s="9">
         <f t="shared" si="6"/>
         <v>7981.9627748246421</v>
       </c>
-      <c r="AD9" s="9">
+      <c r="AH9" s="9">
         <f t="shared" si="6"/>
         <v>8061.7824025728887</v>
       </c>
-      <c r="AE9" s="9">
+      <c r="AI9" s="9">
         <f t="shared" si="6"/>
         <v>8142.4002265986173</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:35">
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1710,75 +1735,75 @@
         <f>+J$9*(I10/I$9)</f>
         <v>2012.2884665451704</v>
       </c>
-      <c r="M10" s="1">
+      <c r="Q10" s="1">
         <v>2474</v>
       </c>
-      <c r="N10" s="1">
+      <c r="R10" s="1">
         <v>3075</v>
       </c>
-      <c r="O10" s="1">
+      <c r="S10" s="1">
         <v>4694</v>
       </c>
-      <c r="P10" s="1">
+      <c r="T10" s="1">
         <v>6346</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="U10" s="1">
         <v>3931</v>
       </c>
-      <c r="R10" s="1">
+      <c r="V10" s="1">
         <v>1748</v>
       </c>
-      <c r="S10" s="1">
+      <c r="W10" s="1">
         <v>3270</v>
       </c>
-      <c r="T10" s="1">
+      <c r="X10" s="1">
         <v>8915</v>
       </c>
-      <c r="U10" s="1">
+      <c r="Y10" s="1">
         <v>11877</v>
       </c>
-      <c r="V10" s="1">
+      <c r="Z10" s="1">
         <f>SUM(G10:J10)</f>
         <v>7443.2884665451702</v>
       </c>
-      <c r="W10" s="1">
-        <f>+W$9*(V10/V$9)</f>
+      <c r="AA10" s="1">
+        <f>+AA$9*(Z10/Z$9)</f>
         <v>3808.6995574471425</v>
       </c>
-      <c r="X10" s="1">
-        <f t="shared" ref="X10:AE10" si="7">+X$9*(W10/W$9)</f>
+      <c r="AB10" s="1">
+        <f t="shared" ref="AB10:AI10" si="7">+AB$9*(AA10/AA$9)</f>
         <v>3846.7865530216141</v>
       </c>
-      <c r="Y10" s="1">
+      <c r="AC10" s="1">
         <f t="shared" si="7"/>
         <v>3885.2544185518304</v>
       </c>
-      <c r="Z10" s="1">
+      <c r="AD10" s="1">
         <f t="shared" si="7"/>
         <v>3924.106962737349</v>
       </c>
-      <c r="AA10" s="1">
+      <c r="AE10" s="1">
         <f t="shared" si="7"/>
         <v>3963.3480323647223</v>
       </c>
-      <c r="AB10" s="1">
+      <c r="AF10" s="1">
         <f t="shared" si="7"/>
         <v>4002.9815126883695</v>
       </c>
-      <c r="AC10" s="1">
+      <c r="AG10" s="1">
         <f t="shared" si="7"/>
         <v>4043.0113278152535</v>
       </c>
-      <c r="AD10" s="1">
+      <c r="AH10" s="1">
         <f t="shared" si="7"/>
         <v>4083.441441093406</v>
       </c>
-      <c r="AE10" s="1">
+      <c r="AI10" s="1">
         <f t="shared" si="7"/>
         <v>4124.2758555043401</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:35">
       <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1808,75 +1833,75 @@
         <f>+J$9*(I11/I$9)</f>
         <v>2134.96485290289</v>
       </c>
-      <c r="M11" s="1">
+      <c r="Q11" s="1">
         <v>27108</v>
       </c>
-      <c r="N11" s="1">
+      <c r="R11" s="1">
         <v>18086</v>
       </c>
-      <c r="O11" s="1">
+      <c r="S11" s="1">
         <v>8158</v>
       </c>
-      <c r="P11" s="1">
+      <c r="T11" s="1">
         <v>4129</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="U11" s="1">
         <v>4182</v>
       </c>
-      <c r="R11" s="1">
+      <c r="V11" s="1">
         <v>8289</v>
       </c>
-      <c r="S11" s="1">
+      <c r="W11" s="1">
         <v>11471</v>
       </c>
-      <c r="T11" s="1">
+      <c r="X11" s="1">
         <v>19768</v>
       </c>
-      <c r="U11" s="1">
+      <c r="Y11" s="1">
         <v>14398</v>
       </c>
-      <c r="V11" s="1">
-        <f t="shared" ref="V11:V14" si="8">SUM(G11:J11)</f>
+      <c r="Z11" s="1">
+        <f t="shared" ref="Z11:Z14" si="8">SUM(G11:J11)</f>
         <v>9771.9648529028891</v>
       </c>
-      <c r="W11" s="1">
-        <f>+W$9*(V11/V$9)</f>
+      <c r="AA11" s="1">
+        <f>+AA$9*(Z11/Z$9)</f>
         <v>5000.2735186098944</v>
       </c>
-      <c r="X11" s="1">
-        <f t="shared" ref="X11:AE11" si="9">+X$9*(W11/W$9)</f>
+      <c r="AB11" s="1">
+        <f t="shared" ref="AB11:AI11" si="9">+AB$9*(AA11/AA$9)</f>
         <v>5050.2762537959934</v>
       </c>
-      <c r="Y11" s="1">
+      <c r="AC11" s="1">
         <f t="shared" si="9"/>
         <v>5100.7790163339532</v>
       </c>
-      <c r="Z11" s="1">
+      <c r="AD11" s="1">
         <f t="shared" si="9"/>
         <v>5151.7868064972936</v>
       </c>
-      <c r="AA11" s="1">
+      <c r="AE11" s="1">
         <f t="shared" si="9"/>
         <v>5203.304674562266</v>
       </c>
-      <c r="AB11" s="1">
+      <c r="AF11" s="1">
         <f t="shared" si="9"/>
         <v>5255.3377213078884</v>
       </c>
-      <c r="AC11" s="1">
+      <c r="AG11" s="1">
         <f t="shared" si="9"/>
         <v>5307.8910985209677</v>
       </c>
-      <c r="AD11" s="1">
+      <c r="AH11" s="1">
         <f t="shared" si="9"/>
         <v>5360.970009506178</v>
       </c>
-      <c r="AE11" s="1">
+      <c r="AI11" s="1">
         <f t="shared" si="9"/>
         <v>5414.5797096012393</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:35">
       <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1906,75 +1931,75 @@
         <f>+J$9*(I12/I$9)</f>
         <v>2323.9260609216349</v>
       </c>
-      <c r="M12" s="1">
+      <c r="Q12" s="1">
         <v>6299</v>
       </c>
-      <c r="N12" s="1">
+      <c r="R12" s="1">
         <v>5693</v>
       </c>
-      <c r="O12" s="1">
+      <c r="S12" s="1">
         <v>4702</v>
       </c>
-      <c r="P12" s="1">
+      <c r="T12" s="1">
         <v>4095</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="U12" s="1">
         <v>4016</v>
       </c>
-      <c r="R12" s="1">
+      <c r="V12" s="1">
         <v>7198</v>
       </c>
-      <c r="S12" s="1">
+      <c r="W12" s="1">
         <v>7016</v>
       </c>
-      <c r="T12" s="1">
+      <c r="X12" s="1">
         <v>11108</v>
       </c>
-      <c r="U12" s="1">
+      <c r="Y12" s="1">
         <v>8505</v>
       </c>
-      <c r="V12" s="1">
+      <c r="Z12" s="1">
         <f t="shared" si="8"/>
         <v>8915.9260609216344</v>
       </c>
-      <c r="W12" s="1">
-        <f>+W$9*(V12/V$9)</f>
+      <c r="AA12" s="1">
+        <f>+AA$9*(Z12/Z$9)</f>
         <v>4562.242051358443</v>
       </c>
-      <c r="X12" s="1">
-        <f t="shared" ref="X12:AE12" si="10">+X$9*(W12/W$9)</f>
+      <c r="AB12" s="1">
+        <f t="shared" ref="AB12:AI12" si="10">+AB$9*(AA12/AA$9)</f>
         <v>4607.864471872027</v>
       </c>
-      <c r="Y12" s="1">
+      <c r="AC12" s="1">
         <f t="shared" si="10"/>
         <v>4653.9431165907481</v>
       </c>
-      <c r="Z12" s="1">
+      <c r="AD12" s="1">
         <f t="shared" si="10"/>
         <v>4700.4825477566555</v>
       </c>
-      <c r="AA12" s="1">
+      <c r="AE12" s="1">
         <f t="shared" si="10"/>
         <v>4747.4873732342221</v>
       </c>
-      <c r="AB12" s="1">
+      <c r="AF12" s="1">
         <f t="shared" si="10"/>
         <v>4794.9622469665646</v>
       </c>
-      <c r="AC12" s="1">
+      <c r="AG12" s="1">
         <f t="shared" si="10"/>
         <v>4842.9118694362305</v>
       </c>
-      <c r="AD12" s="1">
+      <c r="AH12" s="1">
         <f t="shared" si="10"/>
         <v>4891.3409881305934</v>
       </c>
-      <c r="AE12" s="1">
+      <c r="AI12" s="1">
         <f t="shared" si="10"/>
         <v>4940.254398011899</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:35">
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
@@ -2010,84 +2035,84 @@
         <f>+J9-SUM(J10:J12)</f>
         <v>-2671.1793803696946</v>
       </c>
-      <c r="M13" s="1">
-        <f t="shared" ref="M13:U13" si="11">+M9-SUM(M10:M12)</f>
+      <c r="Q13" s="1">
+        <f t="shared" ref="Q13:Y13" si="11">+Q9-SUM(Q10:Q12)</f>
         <v>-31491</v>
       </c>
-      <c r="N13" s="1">
+      <c r="R13" s="1">
         <f t="shared" si="11"/>
         <v>-20830</v>
       </c>
-      <c r="O13" s="1">
+      <c r="S13" s="1">
         <f t="shared" si="11"/>
         <v>-8712</v>
       </c>
-      <c r="P13" s="1">
+      <c r="T13" s="1">
         <f t="shared" si="11"/>
         <v>2030</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="U13" s="1">
         <f t="shared" si="11"/>
         <v>-2043</v>
       </c>
-      <c r="R13" s="1">
+      <c r="V13" s="1">
         <f t="shared" si="11"/>
         <v>-8145</v>
       </c>
-      <c r="S13" s="1">
+      <c r="W13" s="1">
         <f t="shared" si="11"/>
         <v>-16078</v>
       </c>
-      <c r="T13" s="1">
+      <c r="X13" s="1">
         <f t="shared" si="11"/>
         <v>-24923</v>
       </c>
-      <c r="U13" s="1">
+      <c r="Y13" s="1">
         <f t="shared" si="11"/>
         <v>-21031</v>
       </c>
-      <c r="V13" s="1">
+      <c r="Z13" s="1">
         <f t="shared" si="8"/>
         <v>-11436.179380369695</v>
       </c>
-      <c r="W13" s="1">
-        <f>+W9-SUM(W10:W12)</f>
+      <c r="AA13" s="1">
+        <f>+AA9-SUM(AA10:AA12)</f>
         <v>-5851.8451274154786</v>
       </c>
-      <c r="X13" s="1">
-        <f t="shared" ref="X13:AE13" si="12">+X9-SUM(X10:X12)</f>
+      <c r="AB13" s="1">
+        <f t="shared" ref="AB13:AI13" si="12">+AB9-SUM(AB10:AB12)</f>
         <v>-5910.3635786896366</v>
       </c>
-      <c r="Y13" s="1">
+      <c r="AC13" s="1">
         <f t="shared" si="12"/>
         <v>-5969.4672144765309</v>
       </c>
-      <c r="Z13" s="1">
+      <c r="AD13" s="1">
         <f t="shared" si="12"/>
         <v>-6029.1618866212975</v>
       </c>
-      <c r="AA13" s="1">
+      <c r="AE13" s="1">
         <f t="shared" si="12"/>
         <v>-6089.4535054875105</v>
       </c>
-      <c r="AB13" s="1">
+      <c r="AF13" s="1">
         <f t="shared" si="12"/>
         <v>-6150.3480405423861</v>
       </c>
-      <c r="AC13" s="1">
+      <c r="AG13" s="1">
         <f t="shared" si="12"/>
         <v>-6211.8515209478101</v>
       </c>
-      <c r="AD13" s="1">
+      <c r="AH13" s="1">
         <f t="shared" si="12"/>
         <v>-6273.9700361572895</v>
       </c>
-      <c r="AE13" s="1">
+      <c r="AI13" s="1">
         <f t="shared" si="12"/>
         <v>-6336.7097365188611</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:35">
       <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
@@ -2117,83 +2142,83 @@
         <f>+J$9*(I14/I$9)</f>
         <v>-15.829211142931531</v>
       </c>
-      <c r="M14" s="1">
+      <c r="Q14" s="1">
         <v>86</v>
       </c>
-      <c r="N14" s="1">
+      <c r="R14" s="1">
         <f>687+48</f>
         <v>735</v>
       </c>
-      <c r="O14" s="1">
+      <c r="S14" s="1">
         <f>+-927+59</f>
         <v>-868</v>
       </c>
-      <c r="P14" s="1">
+      <c r="T14" s="1">
         <f>+-582+12</f>
         <v>-570</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="U14" s="1">
         <f>+-220+103</f>
         <v>-117</v>
       </c>
-      <c r="R14" s="1">
+      <c r="V14" s="1">
         <f>+-2101-77</f>
         <v>-2178</v>
       </c>
-      <c r="S14" s="1">
+      <c r="W14" s="1">
         <f>+-2979+44</f>
         <v>-2935</v>
       </c>
-      <c r="T14" s="1">
+      <c r="X14" s="1">
         <f>+-16-89</f>
         <v>-105</v>
       </c>
-      <c r="U14" s="1">
+      <c r="Y14" s="1">
         <f>+-21+358</f>
         <v>337</v>
       </c>
-      <c r="V14" s="1">
+      <c r="Z14" s="1">
         <f t="shared" si="8"/>
         <v>-26.829211142931531</v>
       </c>
-      <c r="W14" s="1">
-        <f>+W13*(V14/V13)</f>
+      <c r="AA14" s="1">
+        <f>+AA13*(Z14/Z13)</f>
         <v>-13.728395058987754</v>
       </c>
-      <c r="X14" s="1">
-        <f t="shared" ref="X14:AE14" si="13">+X13*(W14/W13)</f>
+      <c r="AB14" s="1">
+        <f t="shared" ref="AB14:AI14" si="13">+AB13*(AA14/AA13)</f>
         <v>-13.86567900957764</v>
       </c>
-      <c r="Y14" s="1">
+      <c r="AC14" s="1">
         <f t="shared" si="13"/>
         <v>-14.004335799673411</v>
       </c>
-      <c r="Z14" s="1">
+      <c r="AD14" s="1">
         <f t="shared" si="13"/>
         <v>-14.144379157670148</v>
       </c>
-      <c r="AA14" s="1">
+      <c r="AE14" s="1">
         <f t="shared" si="13"/>
         <v>-14.28582294924685</v>
       </c>
-      <c r="AB14" s="1">
+      <c r="AF14" s="1">
         <f t="shared" si="13"/>
         <v>-14.428681178739319</v>
       </c>
-      <c r="AC14" s="1">
+      <c r="AG14" s="1">
         <f t="shared" si="13"/>
         <v>-14.572967990526713</v>
       </c>
-      <c r="AD14" s="1">
+      <c r="AH14" s="1">
         <f t="shared" si="13"/>
         <v>-14.718697670431983</v>
       </c>
-      <c r="AE14" s="1">
+      <c r="AI14" s="1">
         <f t="shared" si="13"/>
         <v>-14.8658846471363</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:35">
       <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
@@ -2229,84 +2254,84 @@
         <f>+SUM(J13:J14)</f>
         <v>-2687.008591512626</v>
       </c>
-      <c r="M15" s="1">
-        <f t="shared" ref="M15:W15" si="14">+SUM(M13:M14)</f>
+      <c r="Q15" s="1">
+        <f t="shared" ref="Q15:AA15" si="14">+SUM(Q13:Q14)</f>
         <v>-31405</v>
       </c>
-      <c r="N15" s="1">
+      <c r="R15" s="1">
         <f t="shared" si="14"/>
         <v>-20095</v>
       </c>
-      <c r="O15" s="1">
+      <c r="S15" s="1">
         <f t="shared" si="14"/>
         <v>-9580</v>
       </c>
-      <c r="P15" s="1">
+      <c r="T15" s="1">
         <f t="shared" si="14"/>
         <v>1460</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="U15" s="1">
         <f t="shared" si="14"/>
         <v>-2160</v>
       </c>
-      <c r="R15" s="1">
+      <c r="V15" s="1">
         <f t="shared" si="14"/>
         <v>-10323</v>
       </c>
-      <c r="S15" s="1">
+      <c r="W15" s="1">
         <f t="shared" si="14"/>
         <v>-19013</v>
       </c>
-      <c r="T15" s="1">
+      <c r="X15" s="1">
         <f t="shared" si="14"/>
         <v>-25028</v>
       </c>
-      <c r="U15" s="1">
+      <c r="Y15" s="1">
         <f t="shared" si="14"/>
         <v>-20694</v>
       </c>
-      <c r="V15" s="1">
+      <c r="Z15" s="1">
         <f t="shared" si="14"/>
         <v>-11463.008591512626</v>
       </c>
-      <c r="W15" s="1">
+      <c r="AA15" s="1">
         <f t="shared" si="14"/>
         <v>-5865.5735224744667</v>
       </c>
-      <c r="X15" s="1">
-        <f t="shared" ref="X15:AE15" si="15">+SUM(X13:X14)</f>
+      <c r="AB15" s="1">
+        <f t="shared" ref="AB15:AI15" si="15">+SUM(AB13:AB14)</f>
         <v>-5924.229257699214</v>
       </c>
-      <c r="Y15" s="1">
+      <c r="AC15" s="1">
         <f t="shared" si="15"/>
         <v>-5983.4715502762047</v>
       </c>
-      <c r="Z15" s="1">
+      <c r="AD15" s="1">
         <f t="shared" si="15"/>
         <v>-6043.3062657789678</v>
       </c>
-      <c r="AA15" s="1">
+      <c r="AE15" s="1">
         <f t="shared" si="15"/>
         <v>-6103.7393284367572</v>
       </c>
-      <c r="AB15" s="1">
+      <c r="AF15" s="1">
         <f t="shared" si="15"/>
         <v>-6164.7767217211258</v>
       </c>
-      <c r="AC15" s="1">
+      <c r="AG15" s="1">
         <f t="shared" si="15"/>
         <v>-6226.4244889383372</v>
       </c>
-      <c r="AD15" s="1">
+      <c r="AH15" s="1">
         <f t="shared" si="15"/>
         <v>-6288.6887338277211</v>
       </c>
-      <c r="AE15" s="1">
+      <c r="AI15" s="1">
         <f t="shared" si="15"/>
         <v>-6351.5756211659973</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:35">
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -2315,12 +2340,12 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="2:33">
+    <row r="17" spans="2:37">
       <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="2:33" s="6" customFormat="1">
+    <row r="18" spans="2:37" s="6" customFormat="1">
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
@@ -2340,61 +2365,45 @@
         <f t="shared" si="16"/>
         <v>1.5626702997275204</v>
       </c>
-      <c r="N18" s="6">
-        <f t="shared" ref="N18:O18" si="17">+N7/M7-1</f>
+      <c r="R18" s="6">
+        <f t="shared" ref="R18:S18" si="17">+R7/Q7-1</f>
         <v>0.91833333333333322</v>
       </c>
-      <c r="O18" s="6">
+      <c r="S18" s="6">
         <f t="shared" si="17"/>
         <v>0.70134665508253691</v>
       </c>
-      <c r="P18" s="6">
-        <f t="shared" ref="P18:V20" si="18">+P7/O7-1</f>
+      <c r="T18" s="6">
+        <f t="shared" ref="T18:Z20" si="18">+T7/S7-1</f>
         <v>0.92174135069577434</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="U18" s="6">
         <f t="shared" si="18"/>
         <v>-0.37706769414734609</v>
       </c>
-      <c r="R18" s="6">
+      <c r="V18" s="6">
         <f t="shared" si="18"/>
         <v>-0.83576836941452493</v>
       </c>
-      <c r="S18" s="6">
+      <c r="W18" s="6">
         <f t="shared" si="18"/>
         <v>2.1857142857142855</v>
       </c>
-      <c r="T18" s="6">
+      <c r="X18" s="6">
         <f t="shared" si="18"/>
         <v>1.8942111699959234</v>
       </c>
-      <c r="U18" s="6">
+      <c r="Y18" s="6">
         <f t="shared" si="18"/>
         <v>-9.4795408127332892E-2</v>
       </c>
-      <c r="V18" s="6">
+      <c r="Z18" s="6">
         <f t="shared" si="18"/>
         <v>0.11709328561425347</v>
       </c>
-      <c r="W18" s="6">
-        <f t="shared" ref="W18:AE18" si="19">+W7/V7-1</f>
+      <c r="AA18" s="6">
+        <f t="shared" ref="AA18:AI18" si="19">+AA7/Z7-1</f>
         <v>-0.5</v>
-      </c>
-      <c r="X18" s="6">
-        <f t="shared" si="19"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Y18" s="6">
-        <f t="shared" si="19"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Z18" s="6">
-        <f t="shared" si="19"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AA18" s="6">
-        <f t="shared" si="19"/>
-        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB18" s="6">
         <f t="shared" si="19"/>
@@ -2412,8 +2421,24 @@
         <f t="shared" si="19"/>
         <v>1.0000000000000009E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:33" s="6" customFormat="1">
+      <c r="AF18" s="6">
+        <f t="shared" si="19"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG18" s="6">
+        <f t="shared" si="19"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH18" s="6">
+        <f t="shared" si="19"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI18" s="6">
+        <f t="shared" si="19"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:37" s="6" customFormat="1">
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
@@ -2433,60 +2458,44 @@
         <f t="shared" si="16"/>
         <v>-0.89560439560439564</v>
       </c>
-      <c r="N19" s="6">
-        <f t="shared" ref="N19:O19" si="20">+N8/M8-1</f>
+      <c r="R19" s="6">
+        <f t="shared" ref="R19:S19" si="20">+R8/Q8-1</f>
         <v>-0.28643216080402012</v>
       </c>
-      <c r="O19" s="6">
+      <c r="S19" s="6">
         <f t="shared" si="20"/>
         <v>-0.28943661971830981</v>
       </c>
-      <c r="P19" s="6">
+      <c r="T19" s="6">
         <f t="shared" si="18"/>
         <v>0.53320118929633309</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="U19" s="6">
         <f t="shared" si="18"/>
         <v>-0.54169360051713</v>
       </c>
-      <c r="R19" s="6">
+      <c r="V19" s="6">
         <f t="shared" si="18"/>
         <v>9.6488011283497883</v>
       </c>
-      <c r="S19" s="6">
+      <c r="W19" s="6">
         <f t="shared" si="18"/>
         <v>-0.89761589403973507</v>
       </c>
-      <c r="T19" s="6">
+      <c r="X19" s="6">
         <f t="shared" si="18"/>
         <v>-0.13454075032341528</v>
       </c>
-      <c r="U19" s="6">
+      <c r="Y19" s="6">
         <f t="shared" si="18"/>
         <v>0.33931240657698059</v>
       </c>
-      <c r="V19" s="6">
+      <c r="Z19" s="6">
         <f t="shared" si="18"/>
         <v>-0.6238839285714286</v>
       </c>
-      <c r="W19" s="6">
-        <f t="shared" ref="W19:AE19" si="21">+W8/V8-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="X19" s="6">
-        <f t="shared" si="21"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Y19" s="6">
-        <f t="shared" si="21"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Z19" s="6">
-        <f t="shared" si="21"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AA19" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="AA19:AI19" si="21">+AA8/Z8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB19" s="6">
@@ -2505,8 +2514,24 @@
         <f t="shared" si="21"/>
         <v>1.0000000000000009E-2</v>
       </c>
-    </row>
-    <row r="20" spans="2:33" s="8" customFormat="1">
+      <c r="AF19" s="6">
+        <f t="shared" si="21"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG19" s="6">
+        <f t="shared" si="21"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH19" s="6">
+        <f t="shared" si="21"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI19" s="6">
+        <f t="shared" si="21"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:37" s="8" customFormat="1">
       <c r="B20" s="4" t="s">
         <v>20</v>
       </c>
@@ -2526,61 +2551,45 @@
         <f t="shared" si="16"/>
         <v>1.0742358078602621</v>
       </c>
-      <c r="N20" s="6">
-        <f t="shared" ref="N20:O20" si="22">+N9/M9-1</f>
+      <c r="R20" s="6">
+        <f t="shared" ref="R20:S20" si="22">+R9/Q9-1</f>
         <v>0.37220956719817777</v>
       </c>
-      <c r="O20" s="6">
+      <c r="S20" s="6">
         <f t="shared" si="22"/>
         <v>0.46779548472775567</v>
       </c>
-      <c r="P20" s="6">
+      <c r="T20" s="6">
         <f t="shared" si="18"/>
         <v>0.87740330242026698</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="U20" s="6">
         <f t="shared" si="18"/>
         <v>-0.39240963855421684</v>
       </c>
-      <c r="R20" s="6">
+      <c r="V20" s="6">
         <f t="shared" si="18"/>
         <v>-9.8750743604997027E-2</v>
       </c>
-      <c r="S20" s="6">
+      <c r="W20" s="6">
         <f t="shared" si="18"/>
         <v>-0.37524752475247525</v>
       </c>
-      <c r="T20" s="6">
+      <c r="X20" s="6">
         <f t="shared" si="18"/>
         <v>1.6180665610142633</v>
       </c>
-      <c r="U20" s="6">
+      <c r="Y20" s="6">
         <f t="shared" si="18"/>
         <v>-7.5262308313155724E-2</v>
       </c>
-      <c r="V20" s="6">
+      <c r="Z20" s="6">
         <f t="shared" si="18"/>
         <v>6.8805004000290992E-2</v>
       </c>
-      <c r="W20" s="6">
-        <f t="shared" ref="W20:AE20" si="23">+W9/V9-1</f>
+      <c r="AA20" s="6">
+        <f t="shared" ref="AA20:AI20" si="23">+AA9/Z9-1</f>
         <v>-0.48830418509697182</v>
-      </c>
-      <c r="X20" s="6">
-        <f t="shared" si="23"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Y20" s="6">
-        <f t="shared" si="23"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Z20" s="6">
-        <f t="shared" si="23"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AA20" s="6">
-        <f t="shared" si="23"/>
-        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="23"/>
@@ -2598,8 +2607,24 @@
         <f t="shared" si="23"/>
         <v>1.0000000000000009E-2</v>
       </c>
-    </row>
-    <row r="21" spans="2:33" s="6" customFormat="1">
+      <c r="AF20" s="6">
+        <f t="shared" si="23"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG20" s="6">
+        <f t="shared" si="23"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH20" s="6">
+        <f t="shared" si="23"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI20" s="6">
+        <f t="shared" si="23"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:37" s="6" customFormat="1">
       <c r="B21" s="6" t="s">
         <v>30</v>
       </c>
@@ -2635,61 +2660,45 @@
         <f t="shared" ref="J21" si="25">(J9-J10) / J9</f>
         <v>0.47045040354074463</v>
       </c>
-      <c r="M21" s="6">
-        <f t="shared" ref="M21" si="26">(M9-M10) / M9</f>
+      <c r="Q21" s="6">
+        <f t="shared" ref="Q21" si="26">(Q9-Q10) / Q9</f>
         <v>0.43644646924829156</v>
       </c>
-      <c r="N21" s="6">
-        <f t="shared" ref="N21:U21" si="27">(N9-N10) / N9</f>
+      <c r="R21" s="6">
+        <f t="shared" ref="R21:Y21" si="27">(R9-R10) / R9</f>
         <v>0.48954183266932272</v>
       </c>
-      <c r="O21" s="6">
+      <c r="S21" s="6">
         <f t="shared" si="27"/>
         <v>0.46912463243610042</v>
       </c>
-      <c r="P21" s="6">
+      <c r="T21" s="6">
         <f t="shared" si="27"/>
         <v>0.61771084337349402</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="U21" s="6">
         <f t="shared" si="27"/>
         <v>0.61025183422565932</v>
       </c>
-      <c r="R21" s="6">
+      <c r="V21" s="6">
         <f t="shared" si="27"/>
         <v>0.80770077007700769</v>
       </c>
-      <c r="S21" s="6">
+      <c r="W21" s="6">
         <f t="shared" si="27"/>
         <v>0.42419440042260964</v>
       </c>
-      <c r="T21" s="6">
+      <c r="X21" s="6">
         <f t="shared" si="27"/>
         <v>0.40039009954264193</v>
       </c>
-      <c r="U21" s="6">
+      <c r="Y21" s="6">
         <f t="shared" si="27"/>
         <v>0.13615535675321841</v>
       </c>
-      <c r="V21" s="6">
-        <f t="shared" ref="V21:AE21" si="28">(V9-V10) / V9</f>
+      <c r="Z21" s="6">
+        <f t="shared" ref="Z21:AI21" si="28">(Z9-Z10) / Z9</f>
         <v>0.49348156062979448</v>
-      </c>
-      <c r="W21" s="6">
-        <f t="shared" si="28"/>
-        <v>0.49348156062979442</v>
-      </c>
-      <c r="X21" s="6">
-        <f t="shared" si="28"/>
-        <v>0.49348156062979442</v>
-      </c>
-      <c r="Y21" s="6">
-        <f t="shared" si="28"/>
-        <v>0.49348156062979442</v>
-      </c>
-      <c r="Z21" s="6">
-        <f t="shared" si="28"/>
-        <v>0.49348156062979442</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="28"/>
@@ -2709,16 +2718,32 @@
       </c>
       <c r="AE21" s="6">
         <f t="shared" si="28"/>
+        <v>0.49348156062979442</v>
+      </c>
+      <c r="AF21" s="6">
+        <f t="shared" si="28"/>
+        <v>0.49348156062979442</v>
+      </c>
+      <c r="AG21" s="6">
+        <f t="shared" si="28"/>
+        <v>0.49348156062979442</v>
+      </c>
+      <c r="AH21" s="6">
+        <f t="shared" si="28"/>
+        <v>0.49348156062979442</v>
+      </c>
+      <c r="AI21" s="6">
+        <f t="shared" si="28"/>
         <v>0.49348156062979437</v>
       </c>
     </row>
-    <row r="22" spans="2:33" s="6" customFormat="1"/>
-    <row r="23" spans="2:33" s="6" customFormat="1">
+    <row r="22" spans="2:37" s="6" customFormat="1"/>
+    <row r="23" spans="2:37" s="6" customFormat="1">
       <c r="B23" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="2:33" s="6" customFormat="1">
+    <row r="24" spans="2:37" s="6" customFormat="1">
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
@@ -2750,60 +2775,44 @@
         <f t="shared" si="29"/>
         <v>0.52954959645925537</v>
       </c>
-      <c r="M24" s="6">
-        <f>+M10/M$9</f>
+      <c r="Q24" s="6">
+        <f>+Q10/Q$9</f>
         <v>0.56355353075170844</v>
       </c>
-      <c r="N24" s="6">
-        <f t="shared" ref="N24:U24" si="30">+N10/N$9</f>
+      <c r="R24" s="6">
+        <f t="shared" ref="R24:Y24" si="30">+R10/R$9</f>
         <v>0.51045816733067728</v>
       </c>
-      <c r="O24" s="6">
+      <c r="S24" s="6">
         <f t="shared" si="30"/>
         <v>0.53087536756389953</v>
       </c>
-      <c r="P24" s="6">
+      <c r="T24" s="6">
         <f t="shared" si="30"/>
         <v>0.38228915662650603</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="U24" s="6">
         <f t="shared" si="30"/>
         <v>0.38974816577434068</v>
       </c>
-      <c r="R24" s="6">
+      <c r="V24" s="6">
         <f t="shared" si="30"/>
         <v>0.19229922992299231</v>
       </c>
-      <c r="S24" s="6">
+      <c r="W24" s="6">
         <f t="shared" si="30"/>
         <v>0.57580559957739041</v>
       </c>
-      <c r="T24" s="6">
+      <c r="X24" s="6">
         <f t="shared" si="30"/>
         <v>0.59960990045735807</v>
       </c>
-      <c r="U24" s="6">
+      <c r="Y24" s="6">
         <f t="shared" si="30"/>
         <v>0.86384464324678156</v>
       </c>
-      <c r="V24" s="6">
-        <f t="shared" ref="V24:AE24" si="31">+V10/V$9</f>
-        <v>0.50651843937020558</v>
-      </c>
-      <c r="W24" s="6">
-        <f t="shared" si="31"/>
-        <v>0.50651843937020558</v>
-      </c>
-      <c r="X24" s="6">
-        <f t="shared" si="31"/>
-        <v>0.50651843937020558</v>
-      </c>
-      <c r="Y24" s="6">
-        <f t="shared" si="31"/>
-        <v>0.50651843937020558</v>
-      </c>
       <c r="Z24" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="Z24:AI24" si="31">+Z10/Z$9</f>
         <v>0.50651843937020558</v>
       </c>
       <c r="AA24" s="6">
@@ -2826,8 +2835,24 @@
         <f t="shared" si="31"/>
         <v>0.50651843937020558</v>
       </c>
-    </row>
-    <row r="25" spans="2:33" s="6" customFormat="1">
+      <c r="AF24" s="6">
+        <f t="shared" si="31"/>
+        <v>0.50651843937020558</v>
+      </c>
+      <c r="AG24" s="6">
+        <f t="shared" si="31"/>
+        <v>0.50651843937020558</v>
+      </c>
+      <c r="AH24" s="6">
+        <f t="shared" si="31"/>
+        <v>0.50651843937020558</v>
+      </c>
+      <c r="AI24" s="6">
+        <f t="shared" si="31"/>
+        <v>0.50651843937020558</v>
+      </c>
+    </row>
+    <row r="25" spans="2:37" s="6" customFormat="1">
       <c r="B25" s="1" t="s">
         <v>21</v>
       </c>
@@ -2859,64 +2884,48 @@
         <f t="shared" si="29"/>
         <v>0.56183285602707633</v>
       </c>
-      <c r="M25" s="6">
-        <f>+M11/M$9</f>
+      <c r="Q25" s="6">
+        <f>+Q11/Q$9</f>
         <v>6.1749430523917992</v>
       </c>
-      <c r="N25" s="6">
-        <f>+N11/N$9</f>
+      <c r="R25" s="6">
+        <f>+R11/R$9</f>
         <v>3.0023240371845952</v>
       </c>
-      <c r="O25" s="6">
-        <f>+O11/O$9</f>
+      <c r="S25" s="6">
+        <f>+S11/S$9</f>
         <v>0.9226419362135263</v>
       </c>
-      <c r="P25" s="6">
-        <f t="shared" ref="P25:S25" si="32">+P11/P$9</f>
+      <c r="T25" s="6">
+        <f t="shared" ref="T25:W25" si="32">+T11/T$9</f>
         <v>0.24873493975903616</v>
       </c>
-      <c r="Q25" s="6">
+      <c r="U25" s="6">
         <f t="shared" si="32"/>
         <v>0.41463414634146339</v>
       </c>
-      <c r="R25" s="6">
+      <c r="V25" s="6">
         <f t="shared" si="32"/>
         <v>0.91188118811881191</v>
       </c>
-      <c r="S25" s="6">
+      <c r="W25" s="6">
         <f t="shared" si="32"/>
         <v>2.0198978693431942</v>
       </c>
-      <c r="T25" s="6">
-        <f>+T11/T$9</f>
+      <c r="X25" s="6">
+        <f>+X11/X$9</f>
         <v>1.3295668549905839</v>
       </c>
-      <c r="U25" s="6">
-        <f>+U11/U$9</f>
+      <c r="Y25" s="6">
+        <f>+Y11/Y$9</f>
         <v>1.0472034329769437</v>
       </c>
-      <c r="V25" s="6">
-        <f>+V11/V$9</f>
+      <c r="Z25" s="6">
+        <f>+Z11/Z$9</f>
         <v>0.66498569941496355</v>
       </c>
-      <c r="W25" s="6">
-        <f t="shared" ref="W25:AE25" si="33">+W11/W$9</f>
-        <v>0.66498569941496355</v>
-      </c>
-      <c r="X25" s="6">
-        <f t="shared" si="33"/>
-        <v>0.66498569941496355</v>
-      </c>
-      <c r="Y25" s="6">
-        <f t="shared" si="33"/>
-        <v>0.66498569941496355</v>
-      </c>
-      <c r="Z25" s="6">
-        <f t="shared" si="33"/>
-        <v>0.66498569941496355</v>
-      </c>
       <c r="AA25" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="AA25:AI25" si="33">+AA11/AA$9</f>
         <v>0.66498569941496355</v>
       </c>
       <c r="AB25" s="6">
@@ -2935,8 +2944,24 @@
         <f t="shared" si="33"/>
         <v>0.66498569941496355</v>
       </c>
-    </row>
-    <row r="26" spans="2:33" s="6" customFormat="1">
+      <c r="AF25" s="6">
+        <f t="shared" si="33"/>
+        <v>0.66498569941496355</v>
+      </c>
+      <c r="AG25" s="6">
+        <f t="shared" si="33"/>
+        <v>0.66498569941496355</v>
+      </c>
+      <c r="AH25" s="6">
+        <f t="shared" si="33"/>
+        <v>0.66498569941496355</v>
+      </c>
+      <c r="AI25" s="6">
+        <f t="shared" si="33"/>
+        <v>0.66498569941496355</v>
+      </c>
+    </row>
+    <row r="26" spans="2:37" s="6" customFormat="1">
       <c r="B26" s="1" t="s">
         <v>22</v>
       </c>
@@ -2968,95 +2993,95 @@
         <f t="shared" si="29"/>
         <v>0.61155948971621976</v>
       </c>
-      <c r="M26" s="6">
-        <f>+M12/M$9</f>
+      <c r="Q26" s="6">
+        <f>+Q12/Q$9</f>
         <v>1.4348519362186789</v>
       </c>
-      <c r="N26" s="6">
-        <f t="shared" ref="N26:U26" si="34">+N12/N$9</f>
+      <c r="R26" s="6">
+        <f t="shared" ref="R26:Y26" si="34">+R12/R$9</f>
         <v>0.94505312084993365</v>
       </c>
-      <c r="O26" s="6">
+      <c r="S26" s="6">
         <f t="shared" si="34"/>
         <v>0.53178014023976472</v>
       </c>
-      <c r="P26" s="6">
+      <c r="T26" s="6">
         <f t="shared" si="34"/>
         <v>0.24668674698795182</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="U26" s="6">
         <f t="shared" si="34"/>
         <v>0.39817568907396389</v>
       </c>
-      <c r="R26" s="6">
+      <c r="V26" s="6">
         <f t="shared" si="34"/>
         <v>0.79185918591859183</v>
       </c>
-      <c r="S26" s="6">
+      <c r="W26" s="6">
         <f t="shared" si="34"/>
         <v>1.235428772671245</v>
       </c>
-      <c r="T26" s="6">
+      <c r="X26" s="6">
         <f t="shared" si="34"/>
         <v>0.74710788270110307</v>
       </c>
-      <c r="U26" s="6">
+      <c r="Y26" s="6">
         <f t="shared" si="34"/>
         <v>0.61859044294130483</v>
       </c>
-      <c r="V26" s="6">
-        <f t="shared" ref="V26:AE26" si="35">+V12/V$9</f>
+      <c r="Z26" s="6">
+        <f t="shared" ref="Z26:AI26" si="35">+Z12/Z$9</f>
         <v>0.60673195378847466</v>
       </c>
-      <c r="W26" s="6">
+      <c r="AA26" s="6">
         <f t="shared" si="35"/>
         <v>0.60673195378847466</v>
       </c>
-      <c r="X26" s="6">
+      <c r="AB26" s="6">
         <f t="shared" si="35"/>
         <v>0.60673195378847466</v>
       </c>
-      <c r="Y26" s="6">
+      <c r="AC26" s="6">
         <f t="shared" si="35"/>
         <v>0.60673195378847466</v>
       </c>
-      <c r="Z26" s="6">
+      <c r="AD26" s="6">
         <f t="shared" si="35"/>
         <v>0.60673195378847466</v>
-      </c>
-      <c r="AA26" s="6">
-        <f t="shared" si="35"/>
-        <v>0.60673195378847478</v>
-      </c>
-      <c r="AB26" s="6">
-        <f t="shared" si="35"/>
-        <v>0.60673195378847478</v>
-      </c>
-      <c r="AC26" s="6">
-        <f t="shared" si="35"/>
-        <v>0.60673195378847478</v>
-      </c>
-      <c r="AD26" s="6">
-        <f t="shared" si="35"/>
-        <v>0.60673195378847478</v>
       </c>
       <c r="AE26" s="6">
         <f t="shared" si="35"/>
         <v>0.60673195378847478</v>
       </c>
-    </row>
-    <row r="27" spans="2:33" s="6" customFormat="1"/>
-    <row r="28" spans="2:33" s="6" customFormat="1"/>
-    <row r="29" spans="2:33">
-      <c r="AF29" s="1" t="s">
+      <c r="AF26" s="6">
+        <f t="shared" si="35"/>
+        <v>0.60673195378847478</v>
+      </c>
+      <c r="AG26" s="6">
+        <f t="shared" si="35"/>
+        <v>0.60673195378847478</v>
+      </c>
+      <c r="AH26" s="6">
+        <f t="shared" si="35"/>
+        <v>0.60673195378847478</v>
+      </c>
+      <c r="AI26" s="6">
+        <f t="shared" si="35"/>
+        <v>0.60673195378847478</v>
+      </c>
+    </row>
+    <row r="27" spans="2:37" s="6" customFormat="1"/>
+    <row r="28" spans="2:37" s="6" customFormat="1"/>
+    <row r="29" spans="2:37">
+      <c r="AJ29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AG29" s="1">
+      <c r="AK29" s="1">
         <f>+Main!F9*1000</f>
         <v>1529.8659700000001</v>
       </c>
     </row>
-    <row r="30" spans="2:33" s="4" customFormat="1">
+    <row r="30" spans="2:37" s="4" customFormat="1">
       <c r="B30" s="4" t="s">
         <v>49</v>
       </c>
@@ -3088,13 +3113,13 @@
         <f>+I31</f>
         <v>1317</v>
       </c>
-      <c r="U30" s="4">
+      <c r="Y30" s="4">
         <f>+I30</f>
         <v>1317</v>
       </c>
-      <c r="AF30" s="1"/>
-    </row>
-    <row r="31" spans="2:33">
+      <c r="AJ30" s="1"/>
+    </row>
+    <row r="31" spans="2:37">
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
@@ -3120,7 +3145,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="32" spans="2:33">
+    <row r="32" spans="2:37">
       <c r="B32" s="1" t="s">
         <v>41</v>
       </c>
@@ -3660,8 +3685,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="M9" formulaRange="1"/>
-    <ignoredError sqref="F9:F15 J13 V9" formula="1"/>
+    <ignoredError sqref="Q9" formulaRange="1"/>
+    <ignoredError sqref="F9:F15 J13 Z9" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
